--- a/patient_feedback_forms/019_health_story_sharing_authorization_form--patient_feedback_forms.xlsx
+++ b/patient_feedback_forms/019_health_story_sharing_authorization_form--patient_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -623,8 +623,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,12 +652,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'health_story_sharing_3',_'label':_'share_with_organizations',_'type':_'select_one',_'options':_['option_3',_'option_4',_'option_5']}</t>
+          <t>share_with_organizations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'health_story_sharing_3', 'label': 'share_with_organizations', 'type': 'select_one', 'options': ['option_3', 'option_4', 'option_5']}</t>
+          <t>share with organizations</t>
         </is>
       </c>
     </row>
@@ -669,12 +669,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'health_story_sharing_4',_'label':_'how_do_you_want_to_share',_'type':_'select_multiple',_'options':_['option_6',_'option_7',_'option_8']}</t>
+          <t>how_do_you_want_to_share</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'health_story_sharing_4', 'label': 'how_do_you_want_to_share', 'type': 'select_multiple', 'options': ['option_6', 'option_7', 'option_8']}</t>
+          <t>how do you want to share</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'health_story_sharing_5',_'label':_'share_with_family_friends',_'type':_'select_multiple',_'options':_['option_9',_'option_10',_'option_11']}</t>
+          <t>share_with_family_friends</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'health_story_sharing_5', 'label': 'share_with_family_friends', 'type': 'select_multiple', 'options': ['option_9', 'option_10', 'option_11']}</t>
+          <t>share with family friends</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'health_story_sharing_6',_'label':_'when_do_you_want_to_share',_'type':_'date',_'options':_[]}</t>
+          <t>when_do_you_want_to_share</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'health_story_sharing_6', 'label': 'when_do_you_want_to_share', 'type': 'date', 'options': []}</t>
+          <t>when do you want to share</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'health_story_sharing_7',_'label':_'what_is_your_relationship',_'type':_'select_one',_'options':_['option_12',_'option_13',_'option_14']}</t>
+          <t>what_is_your_relationship</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'health_story_sharing_7', 'label': 'what_is_your_relationship', 'type': 'select_one', 'options': ['option_12', 'option_13', 'option_14']}</t>
+          <t>what is your relationship</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'health_story_sharing_8',_'label':_'share_with_healthcare',_'type':_'select_one',_'options':_['option_15',_'option_16',_'option_17']}</t>
+          <t>share_with_healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'health_story_sharing_8', 'label': 'share_with_healthcare', 'type': 'select_one', 'options': ['option_15', 'option_16', 'option_17']}</t>
+          <t>share with healthcare</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'health_story_sharing_9',_'label':_'contact_information',_'type':_'text',_'options':_[]}</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'health_story_sharing_9', 'label': 'contact_information', 'type': 'text', 'options': []}</t>
+          <t>contact information</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'health_story_sharing_10',_'label':_'email',_'type':_'email',_'options':_[]}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'health_story_sharing_10', 'label': 'email', 'type': 'email', 'options': []}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'health_story_sharing_11',_'label':_'phone',_'type':_'phone',_'options':_[]}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'health_story_sharing_11', 'label': 'phone', 'type': 'phone', 'options': []}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'health_story_sharing_12',_'label':_'note',_'type':_'note',_'options':_[]}</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'health_story_sharing_12', 'label': 'note', 'type': 'note', 'options': []}</t>
+          <t>note</t>
         </is>
       </c>
     </row>
